--- a/RACI/RACI-modelo.xlsx
+++ b/RACI/RACI-modelo.xlsx
@@ -1672,11 +1672,11 @@
         </c:ser>
         <c:gapWidth val="90"/>
         <c:overlap val="100"/>
-        <c:axId val="52882600"/>
-        <c:axId val="6406668"/>
+        <c:axId val="8588612"/>
+        <c:axId val="11633398"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="52882600"/>
+        <c:axId val="8588612"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1708,7 +1708,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6406668"/>
+        <c:crossAx val="11633398"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1716,7 +1716,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6406668"/>
+        <c:axId val="11633398"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1756,7 +1756,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52882600"/>
+        <c:crossAx val="8588612"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4474,12 +4474,12 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G6:G13" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Sim, Parcial ou Não" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="H6:H13" type="list">
       <formula1>"Sim,Parcial,Não"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G6:G13" type="date">
-      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
